--- a/artfynd/A 32345-2026 artfynd.xlsx
+++ b/artfynd/A 32345-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136325964</v>
       </c>
       <c r="B2" t="n">
-        <v>92070</v>
+        <v>92076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136325958</v>
       </c>
       <c r="B5" t="n">
-        <v>102084</v>
+        <v>102095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136325962</v>
       </c>
       <c r="B6" t="n">
-        <v>102084</v>
+        <v>102095</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136325968</v>
       </c>
       <c r="B7" t="n">
-        <v>102084</v>
+        <v>102095</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136325960</v>
       </c>
       <c r="B8" t="n">
-        <v>108328</v>
+        <v>108339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136325961</v>
       </c>
       <c r="B9" t="n">
-        <v>108328</v>
+        <v>108339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136325963</v>
       </c>
       <c r="B10" t="n">
-        <v>108328</v>
+        <v>108339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136325966</v>
       </c>
       <c r="B11" t="n">
-        <v>108328</v>
+        <v>108339</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136325969</v>
       </c>
       <c r="B12" t="n">
-        <v>108328</v>
+        <v>108339</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136325970</v>
       </c>
       <c r="B13" t="n">
-        <v>108328</v>
+        <v>108339</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136325965</v>
       </c>
       <c r="B14" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>136325959</v>
       </c>
       <c r="B15" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 32345-2026 artfynd.xlsx
+++ b/artfynd/A 32345-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136325964</v>
       </c>
       <c r="B2" t="n">
-        <v>92076</v>
+        <v>92083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136325967</v>
       </c>
       <c r="B3" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>136325957</v>
       </c>
       <c r="B4" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136325958</v>
       </c>
       <c r="B5" t="n">
-        <v>102095</v>
+        <v>102108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136325962</v>
       </c>
       <c r="B6" t="n">
-        <v>102095</v>
+        <v>102108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136325968</v>
       </c>
       <c r="B7" t="n">
-        <v>102095</v>
+        <v>102108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136325960</v>
       </c>
       <c r="B8" t="n">
-        <v>108339</v>
+        <v>108352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136325961</v>
       </c>
       <c r="B9" t="n">
-        <v>108339</v>
+        <v>108352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136325963</v>
       </c>
       <c r="B10" t="n">
-        <v>108339</v>
+        <v>108352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136325966</v>
       </c>
       <c r="B11" t="n">
-        <v>108339</v>
+        <v>108352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136325969</v>
       </c>
       <c r="B12" t="n">
-        <v>108339</v>
+        <v>108352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136325970</v>
       </c>
       <c r="B13" t="n">
-        <v>108339</v>
+        <v>108352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136325965</v>
       </c>
       <c r="B14" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>136325959</v>
       </c>
       <c r="B15" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 32345-2026 artfynd.xlsx
+++ b/artfynd/A 32345-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136325967</v>
+        <v>136404446</v>
       </c>
       <c r="B3" t="n">
-        <v>57990</v>
+        <v>80579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,42 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hållflon, Dlr</t>
+          <t>Kringelfjorden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384546</v>
+        <v>384497</v>
       </c>
       <c r="R3" t="n">
-        <v>6850639</v>
+        <v>6850542</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,62 +887,67 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Christel Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Christel Andersson</t>
+          <t>Christel Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136325967</t>
+          <t>https://artportalen.se/Sighting/136404446</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136325957</v>
+        <v>136325967</v>
       </c>
       <c r="B4" t="n">
-        <v>58154</v>
+        <v>57990</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hållflon, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384358</v>
+        <v>384546</v>
       </c>
       <c r="R4" t="n">
-        <v>6850555</v>
+        <v>6850639</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,16 +1015,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136325957</t>
+          <t>https://artportalen.se/Sighting/136325967</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136325958</v>
+        <v>136325957</v>
       </c>
       <c r="B5" t="n">
-        <v>102108</v>
+        <v>58154</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220075</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chrysosplenium alternifolium</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384407</v>
+        <v>384358</v>
       </c>
       <c r="R5" t="n">
-        <v>6850573</v>
+        <v>6850555</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>I källmiljö med bristande hänsyn</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,13 +1127,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136325958</t>
+          <t>https://artportalen.se/Sighting/136325957</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136325962</v>
+        <v>136325958</v>
       </c>
       <c r="B6" t="n">
         <v>102108</v>
@@ -1173,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>384446</v>
+        <v>384407</v>
       </c>
       <c r="R6" t="n">
-        <v>6850583</v>
+        <v>6850573</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I källmiljö med bristande hänsyn</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,13 +1244,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136325962</t>
+          <t>https://artportalen.se/Sighting/136325958</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136325968</v>
+        <v>136325962</v>
       </c>
       <c r="B7" t="n">
         <v>102108</v>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>384548</v>
+        <v>384446</v>
       </c>
       <c r="R7" t="n">
-        <v>6850664</v>
+        <v>6850583</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,38 +1356,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136325968</t>
+          <t>https://artportalen.se/Sighting/136325962</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136325960</v>
+        <v>136325968</v>
       </c>
       <c r="B8" t="n">
-        <v>108352</v>
+        <v>102108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220083</v>
+        <v>220075</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>384440</v>
+        <v>384548</v>
       </c>
       <c r="R8" t="n">
-        <v>6850591</v>
+        <v>6850664</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,13 +1468,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136325960</t>
+          <t>https://artportalen.se/Sighting/136325968</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136325961</v>
+        <v>136325960</v>
       </c>
       <c r="B9" t="n">
         <v>108352</v>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>384443</v>
+        <v>384440</v>
       </c>
       <c r="R9" t="n">
-        <v>6850587</v>
+        <v>6850591</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,13 +1580,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136325961</t>
+          <t>https://artportalen.se/Sighting/136325960</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136325963</v>
+        <v>136325961</v>
       </c>
       <c r="B10" t="n">
         <v>108352</v>
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>384453</v>
+        <v>384443</v>
       </c>
       <c r="R10" t="n">
-        <v>6850582</v>
+        <v>6850587</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,13 +1692,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136325963</t>
+          <t>https://artportalen.se/Sighting/136325961</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136325966</v>
+        <v>136325963</v>
       </c>
       <c r="B11" t="n">
         <v>108352</v>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>384526</v>
+        <v>384453</v>
       </c>
       <c r="R11" t="n">
-        <v>6850614</v>
+        <v>6850582</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,13 +1804,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136325966</t>
+          <t>https://artportalen.se/Sighting/136325963</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136325969</v>
+        <v>136325966</v>
       </c>
       <c r="B12" t="n">
         <v>108352</v>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>384553</v>
+        <v>384526</v>
       </c>
       <c r="R12" t="n">
-        <v>6850661</v>
+        <v>6850614</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,13 +1916,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136325969</t>
+          <t>https://artportalen.se/Sighting/136325966</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136325970</v>
+        <v>136325969</v>
       </c>
       <c r="B13" t="n">
         <v>108352</v>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>384466</v>
+        <v>384553</v>
       </c>
       <c r="R13" t="n">
-        <v>6850647</v>
+        <v>6850661</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,16 +2028,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136325970</t>
+          <t>https://artportalen.se/Sighting/136325969</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136325965</v>
+        <v>136325970</v>
       </c>
       <c r="B14" t="n">
-        <v>98189</v>
+        <v>108352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,21 +2045,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220083</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>384509</v>
+        <v>384466</v>
       </c>
       <c r="R14" t="n">
-        <v>6850569</v>
+        <v>6850647</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,16 +2140,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136325965</t>
+          <t>https://artportalen.se/Sighting/136325970</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136325959</v>
+        <v>136404445</v>
       </c>
       <c r="B15" t="n">
-        <v>99133</v>
+        <v>108352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2157,37 +2157,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223049</v>
+        <v>220083</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hållflon, Dlr</t>
+          <t>Kringelfjorden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>384446</v>
+        <v>384456</v>
       </c>
       <c r="R15" t="n">
-        <v>6850583</v>
+        <v>6850577</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,16 +2241,240 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Christel Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Christel Andersson</t>
+          <t>Christel Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136404445</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136325965</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98189</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hållflon, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>384509</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6850569</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Christel Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136325965</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136325959</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99133</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hållflon, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>384446</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6850583</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Christel Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136325959</t>
         </is>
@@ -2272,6 +2496,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32345-2026 artfynd.xlsx
+++ b/artfynd/A 32345-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136325964</v>
       </c>
       <c r="B2" t="n">
-        <v>92083</v>
+        <v>92084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>136325958</v>
       </c>
       <c r="B6" t="n">
-        <v>102108</v>
+        <v>102109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136325962</v>
       </c>
       <c r="B7" t="n">
-        <v>102108</v>
+        <v>102109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136325968</v>
       </c>
       <c r="B8" t="n">
-        <v>102108</v>
+        <v>102109</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136325960</v>
       </c>
       <c r="B9" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136325961</v>
       </c>
       <c r="B10" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136325963</v>
       </c>
       <c r="B11" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136325966</v>
       </c>
       <c r="B12" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136325969</v>
       </c>
       <c r="B13" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136325970</v>
       </c>
       <c r="B14" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>136404445</v>
       </c>
       <c r="B15" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>136325965</v>
       </c>
       <c r="B16" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>136325959</v>
       </c>
       <c r="B17" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32345-2026 artfynd.xlsx
+++ b/artfynd/A 32345-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136325964</v>
       </c>
       <c r="B2" t="n">
-        <v>92084</v>
+        <v>92097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136404446</v>
       </c>
       <c r="B3" t="n">
-        <v>80579</v>
+        <v>80592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136325967</v>
       </c>
       <c r="B4" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136325957</v>
       </c>
       <c r="B5" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>136325958</v>
       </c>
       <c r="B6" t="n">
-        <v>102109</v>
+        <v>102122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136325962</v>
       </c>
       <c r="B7" t="n">
-        <v>102109</v>
+        <v>102122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136325968</v>
       </c>
       <c r="B8" t="n">
-        <v>102109</v>
+        <v>102122</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136325960</v>
       </c>
       <c r="B9" t="n">
-        <v>108353</v>
+        <v>108366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136325961</v>
       </c>
       <c r="B10" t="n">
-        <v>108353</v>
+        <v>108366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136325963</v>
       </c>
       <c r="B11" t="n">
-        <v>108353</v>
+        <v>108366</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136325966</v>
       </c>
       <c r="B12" t="n">
-        <v>108353</v>
+        <v>108366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136325969</v>
       </c>
       <c r="B13" t="n">
-        <v>108353</v>
+        <v>108366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136325970</v>
       </c>
       <c r="B14" t="n">
-        <v>108353</v>
+        <v>108366</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>136404445</v>
       </c>
       <c r="B15" t="n">
-        <v>108353</v>
+        <v>108366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>136325965</v>
       </c>
       <c r="B16" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>136325959</v>
       </c>
       <c r="B17" t="n">
-        <v>99134</v>
+        <v>99147</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32345-2026 artfynd.xlsx
+++ b/artfynd/A 32345-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136325964</v>
       </c>
       <c r="B2" t="n">
-        <v>92097</v>
+        <v>92098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136404446</v>
       </c>
       <c r="B3" t="n">
-        <v>80592</v>
+        <v>80593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>136325958</v>
       </c>
       <c r="B6" t="n">
-        <v>102122</v>
+        <v>102123</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136325962</v>
       </c>
       <c r="B7" t="n">
-        <v>102122</v>
+        <v>102123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136325968</v>
       </c>
       <c r="B8" t="n">
-        <v>102122</v>
+        <v>102123</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136325960</v>
       </c>
       <c r="B9" t="n">
-        <v>108366</v>
+        <v>108367</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136325961</v>
       </c>
       <c r="B10" t="n">
-        <v>108366</v>
+        <v>108367</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136325963</v>
       </c>
       <c r="B11" t="n">
-        <v>108366</v>
+        <v>108367</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136325966</v>
       </c>
       <c r="B12" t="n">
-        <v>108366</v>
+        <v>108367</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136325969</v>
       </c>
       <c r="B13" t="n">
-        <v>108366</v>
+        <v>108367</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136325970</v>
       </c>
       <c r="B14" t="n">
-        <v>108366</v>
+        <v>108367</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>136404445</v>
       </c>
       <c r="B15" t="n">
-        <v>108366</v>
+        <v>108367</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>136325965</v>
       </c>
       <c r="B16" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>136325959</v>
       </c>
       <c r="B17" t="n">
-        <v>99147</v>
+        <v>99148</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
